--- a/MYOREHAB_Data_Dictionary.xlsx
+++ b/MYOREHAB_Data_Dictionary.xlsx
@@ -796,12 +796,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1152,6 +1152,141 @@
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>injuries_description</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>type of injuries</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Participant's sport</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>sport_type</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Type of sport practiced</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>sport_frequency</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Frequency of sport practiced in days in a week</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>temporal_mark</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD HH:MM:SS</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp of form submission or data entry</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/MYOREHAB_Data_Dictionary.xlsx
+++ b/MYOREHAB_Data_Dictionary.xlsx
@@ -15,6 +15,7 @@
     <sheet name="5_Recordings" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="6_EMG_Signals" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="7_Kinematics_3D" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8_Videos_3D" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -890,22 +891,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>acronyms</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Years</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Participant's age</t>
+          <t>acronyms from name and family name</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -917,22 +918,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Years</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Participant's gender</t>
+          <t>Participant's age</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -944,22 +945,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>NUMERIC(5,2)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Kilograms (kg)</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Body weight</t>
+          <t>Participant's gender</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -971,7 +972,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -981,12 +982,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Centimeters (cm)</t>
+          <t>Kilograms (kg)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Body weight</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -998,7 +999,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>fa_circ</t>
+          <t>height</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1013,7 +1014,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Forearm circumference</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1025,22 +1026,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>lateral_dominance</t>
+          <t>fa_circ</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>NUMERIC(5,2)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Centimeters (cm)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Handedness (Right/Left)</t>
+          <t>Forearm circumference</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1052,22 +1053,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>laterality</t>
+          <t>lateral_dominance</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>NUMERIC(5,2)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Laterality index (e.g., Edinburgh Inventory)</t>
+          <t>Handedness (Right/Left)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1079,22 +1080,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>nhpeg_dominant</t>
+          <t>laterality</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>NUMERIC(6,2)</t>
+          <t>NUMERIC(5,2)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Seconds (s)</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NHPT time for dominant hand</t>
+          <t>Laterality index (e.g., Edinburgh Inventory)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1106,7 +1107,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>nhpeg_nondominant</t>
+          <t>nhpeg_dominant</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1121,7 +1122,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NHPT time for non-dominant hand</t>
+          <t>NHPT time for dominant hand</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1133,22 +1134,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>injuries</t>
+          <t>nhpeg_nondominant</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>NUMERIC(6,2)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Seconds (s)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Clinical history or relevant upper-limb injuries</t>
+          <t>NHPT time for non-dominant hand</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1160,12 +1161,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>injuries_description</t>
+          <t>injuries</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1175,7 +1176,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>type of injuries</t>
+          <t>Clinical history or relevant upper-limb injuries</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1187,7 +1188,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>sport</t>
+          <t>injuries_description</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1202,7 +1203,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Participant's sport</t>
+          <t>type of injuries</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1214,7 +1215,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>sport_type</t>
+          <t>sport</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1229,7 +1230,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Type of sport practiced</t>
+          <t>Participant's sport</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1241,7 +1242,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>sport_frequency</t>
+          <t>sport_type</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1256,7 +1257,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Frequency of sport practiced in days in a week</t>
+          <t>Type of sport practiced</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1268,25 +1269,52 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>sport_frequency</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Frequency of sport practiced in days in a week</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>temporal_mark</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Timestamp of form submission or data entry</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1303,7 +1331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1370,7 +1398,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>signal_type</t>
+          <t>center_id</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1380,29 +1408,29 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Alphanumeric</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Signal modality ('EMG' or 'KINEMATICS')</t>
+          <t>References the research center</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>signal_type</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1412,7 +1440,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Manufacturer (e.g., 'In-house UNICAMP')</t>
+          <t>Signal modality ('EMG' or 'KINEMATICS')</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1424,7 +1452,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1439,7 +1467,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Hardware model</t>
+          <t>Manufacturer (e.g., 'In-house UNICAMP')</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1451,7 +1479,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>channel_layout</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1466,7 +1494,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Physical distribution (e.g., '2x64 matrices', '4x32 bands')</t>
+          <t>Hardware model</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1478,25 +1506,52 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>channel_layout</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Physical distribution (e.g., '2x64 matrices', '4x32 bands')</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>total_channels</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Total data channels</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1669,13 +1724,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1809,33 +1864,6 @@
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>file_path</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR(255)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Relative path in 'emg-raw-renamed/' following pattern 'SNNN_PGA.csv'</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1852,12 +1880,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="59" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1892,49 +1920,49 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>task_id</t>
+          <t>emg_id</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Alphanumeric</t>
+          <t>UUID v4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>References the task/trial execution</t>
+          <t>Unique identifier for the EMG signal metadata entry</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>subject_id</t>
+          <t>recording_id</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Alphanumeric</t>
+          <t>UUID v4</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>References the participant</t>
+          <t>References the recording session</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1946,49 +1974,49 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>flex_ch1</t>
+          <t>equipment_id</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>uV / Digital</t>
+          <t>Alphanumeric</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 1 placed over forearm flexor muscles</t>
+          <t>References the EMG acquisition equipment</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>flex_ch2</t>
+          <t>file_path</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>uV / Digital</t>
+          <t>Relative Path</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 2 placed over forearm flexor muscles</t>
+          <t>Relative file path to the raw/renamed sEMG CSV file</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2000,7 +2028,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>flex_ch3</t>
+          <t>flex_ch1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2015,7 +2043,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 3 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 1 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2027,7 +2055,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>flex_ch4</t>
+          <t>flex_ch2</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2042,7 +2070,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 4 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 2 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2054,7 +2082,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>flex_ch5</t>
+          <t>flex_ch3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2069,7 +2097,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 5 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 3 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -2081,7 +2109,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>flex_ch6</t>
+          <t>flex_ch4</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -2096,7 +2124,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 6 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 4 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2108,7 +2136,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>flex_ch7</t>
+          <t>flex_ch5</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2123,7 +2151,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 7 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 5 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2135,7 +2163,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>flex_ch8</t>
+          <t>flex_ch6</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2150,7 +2178,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 8 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 6 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2162,7 +2190,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>flex_ch9</t>
+          <t>flex_ch7</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2177,7 +2205,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 9 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 7 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2189,7 +2217,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>flex_ch10</t>
+          <t>flex_ch8</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2204,7 +2232,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 10 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 8 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2216,7 +2244,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>flex_ch11</t>
+          <t>flex_ch9</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2231,7 +2259,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 11 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 9 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2243,7 +2271,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>flex_ch12</t>
+          <t>flex_ch10</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2258,7 +2286,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 12 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 10 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2298,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>flex_ch13</t>
+          <t>flex_ch11</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2285,7 +2313,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 13 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 11 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2297,7 +2325,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>flex_ch14</t>
+          <t>flex_ch12</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2312,7 +2340,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 14 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 12 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2324,7 +2352,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>flex_ch15</t>
+          <t>flex_ch13</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2339,7 +2367,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 15 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 13 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2351,7 +2379,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>flex_ch16</t>
+          <t>flex_ch14</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2366,7 +2394,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 16 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 14 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2378,7 +2406,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>flex_ch17</t>
+          <t>flex_ch15</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2393,7 +2421,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 17 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 15 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2405,7 +2433,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>flex_ch18</t>
+          <t>flex_ch16</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2420,7 +2448,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 18 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 16 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2432,7 +2460,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>flex_ch19</t>
+          <t>flex_ch17</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2447,7 +2475,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 19 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 17 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2459,7 +2487,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>flex_ch20</t>
+          <t>flex_ch18</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2474,7 +2502,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 20 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 18 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2486,7 +2514,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>flex_ch21</t>
+          <t>flex_ch19</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2501,7 +2529,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 21 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 19 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2513,7 +2541,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>flex_ch22</t>
+          <t>flex_ch20</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2528,7 +2556,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 22 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 20 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2540,7 +2568,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>flex_ch23</t>
+          <t>flex_ch21</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2555,7 +2583,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 23 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 21 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2567,7 +2595,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>flex_ch24</t>
+          <t>flex_ch22</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2582,7 +2610,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 24 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 22 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2594,7 +2622,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>flex_ch25</t>
+          <t>flex_ch23</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2609,7 +2637,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 25 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 23 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2621,7 +2649,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>flex_ch26</t>
+          <t>flex_ch24</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2636,7 +2664,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 26 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 24 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2648,7 +2676,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>flex_ch27</t>
+          <t>flex_ch25</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2663,7 +2691,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 27 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 25 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2675,7 +2703,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>flex_ch28</t>
+          <t>flex_ch26</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2690,7 +2718,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 28 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 26 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2702,7 +2730,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>flex_ch29</t>
+          <t>flex_ch27</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2717,7 +2745,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 29 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 27 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2729,7 +2757,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>flex_ch30</t>
+          <t>flex_ch28</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2744,7 +2772,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 30 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 28 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2756,7 +2784,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>flex_ch31</t>
+          <t>flex_ch29</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2771,7 +2799,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 31 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 29 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2783,7 +2811,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>flex_ch32</t>
+          <t>flex_ch30</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2798,7 +2826,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 32 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 30 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2810,7 +2838,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>flex_ch33</t>
+          <t>flex_ch31</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2825,7 +2853,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 33 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 31 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2837,7 +2865,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>flex_ch34</t>
+          <t>flex_ch32</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2852,7 +2880,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 34 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 32 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2864,7 +2892,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>flex_ch35</t>
+          <t>flex_ch33</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2879,7 +2907,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 35 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 33 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2891,7 +2919,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>flex_ch36</t>
+          <t>flex_ch34</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2906,7 +2934,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 36 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 34 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2918,7 +2946,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>flex_ch37</t>
+          <t>flex_ch35</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2933,7 +2961,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 37 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 35 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2945,7 +2973,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>flex_ch38</t>
+          <t>flex_ch36</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2960,7 +2988,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 38 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 36 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2972,7 +3000,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>flex_ch39</t>
+          <t>flex_ch37</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2987,7 +3015,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 39 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 37 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2999,7 +3027,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>flex_ch40</t>
+          <t>flex_ch38</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -3014,7 +3042,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 40 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 38 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3026,7 +3054,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>flex_ch41</t>
+          <t>flex_ch39</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3041,7 +3069,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 41 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 39 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -3053,7 +3081,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>flex_ch42</t>
+          <t>flex_ch40</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -3068,7 +3096,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 42 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 40 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3080,7 +3108,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>flex_ch43</t>
+          <t>flex_ch41</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3095,7 +3123,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 43 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 41 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3107,7 +3135,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>flex_ch44</t>
+          <t>flex_ch42</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -3122,7 +3150,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 44 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 42 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3134,7 +3162,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>flex_ch45</t>
+          <t>flex_ch43</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3149,7 +3177,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 45 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 43 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3161,7 +3189,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>flex_ch46</t>
+          <t>flex_ch44</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3176,7 +3204,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 46 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 44 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3188,7 +3216,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>flex_ch47</t>
+          <t>flex_ch45</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3203,7 +3231,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 47 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 45 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3215,7 +3243,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>flex_ch48</t>
+          <t>flex_ch46</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3230,7 +3258,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 48 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 46 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3242,7 +3270,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>flex_ch49</t>
+          <t>flex_ch47</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3257,7 +3285,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 49 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 47 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3269,7 +3297,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>flex_ch50</t>
+          <t>flex_ch48</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -3284,7 +3312,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 50 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 48 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3296,7 +3324,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>flex_ch51</t>
+          <t>flex_ch49</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3311,7 +3339,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 51 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 49 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3323,7 +3351,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>flex_ch52</t>
+          <t>flex_ch50</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3338,7 +3366,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 52 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 50 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3350,7 +3378,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>flex_ch53</t>
+          <t>flex_ch51</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3365,7 +3393,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 53 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 51 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3377,7 +3405,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>flex_ch54</t>
+          <t>flex_ch52</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -3392,7 +3420,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 54 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 52 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -3404,7 +3432,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>flex_ch55</t>
+          <t>flex_ch53</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3419,7 +3447,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 55 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 53 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3431,7 +3459,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>flex_ch56</t>
+          <t>flex_ch54</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3446,7 +3474,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 56 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 54 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3458,7 +3486,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>flex_ch57</t>
+          <t>flex_ch55</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3473,7 +3501,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 57 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 55 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3485,7 +3513,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>flex_ch58</t>
+          <t>flex_ch56</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -3500,7 +3528,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 58 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 56 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3512,7 +3540,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>flex_ch59</t>
+          <t>flex_ch57</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3527,7 +3555,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 59 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 57 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3539,7 +3567,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>flex_ch60</t>
+          <t>flex_ch58</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -3554,7 +3582,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 60 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 58 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -3566,7 +3594,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>flex_ch61</t>
+          <t>flex_ch59</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3581,7 +3609,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 61 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 59 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3593,7 +3621,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>flex_ch62</t>
+          <t>flex_ch60</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -3608,7 +3636,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 62 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 60 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -3620,7 +3648,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>flex_ch63</t>
+          <t>flex_ch61</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3635,7 +3663,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 63 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 61 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3647,7 +3675,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>flex_ch64</t>
+          <t>flex_ch62</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -3662,7 +3690,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 64 placed over forearm flexor muscles</t>
+          <t>HD-sEMG channel 62 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3674,7 +3702,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>exte_ch1</t>
+          <t>flex_ch63</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3689,7 +3717,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 1 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 63 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3701,7 +3729,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>exte_ch2</t>
+          <t>flex_ch64</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -3716,7 +3744,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 2 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 64 placed over forearm flexor muscles</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -3728,7 +3756,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>exte_ch3</t>
+          <t>exte_ch1</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3743,7 +3771,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 3 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 1 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3755,7 +3783,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>exte_ch4</t>
+          <t>exte_ch2</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -3770,7 +3798,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 4 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 2 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3782,7 +3810,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>exte_ch5</t>
+          <t>exte_ch3</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3797,7 +3825,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 5 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 3 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3809,7 +3837,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>exte_ch6</t>
+          <t>exte_ch4</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -3824,7 +3852,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 6 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 4 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -3836,7 +3864,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>exte_ch7</t>
+          <t>exte_ch5</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3851,7 +3879,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 7 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 5 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3863,7 +3891,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>exte_ch8</t>
+          <t>exte_ch6</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -3878,7 +3906,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 8 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 6 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -3890,7 +3918,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>exte_ch9</t>
+          <t>exte_ch7</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3905,7 +3933,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 9 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 7 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3917,7 +3945,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>exte_ch10</t>
+          <t>exte_ch8</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -3932,7 +3960,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 10 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 8 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -3944,7 +3972,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>exte_ch11</t>
+          <t>exte_ch9</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3959,7 +3987,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 11 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 9 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3971,7 +3999,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>exte_ch12</t>
+          <t>exte_ch10</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -3986,7 +4014,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 12 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 10 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3998,7 +4026,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>exte_ch13</t>
+          <t>exte_ch11</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4013,7 +4041,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 13 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 11 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -4025,7 +4053,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>exte_ch14</t>
+          <t>exte_ch12</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -4040,7 +4068,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 14 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 12 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -4052,7 +4080,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>exte_ch15</t>
+          <t>exte_ch13</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4067,7 +4095,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 15 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 13 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -4079,7 +4107,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>exte_ch16</t>
+          <t>exte_ch14</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -4094,7 +4122,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 16 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 14 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -4106,7 +4134,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>exte_ch17</t>
+          <t>exte_ch15</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4121,7 +4149,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 17 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 15 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -4133,7 +4161,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>exte_ch18</t>
+          <t>exte_ch16</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -4148,7 +4176,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 18 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 16 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4160,7 +4188,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>exte_ch19</t>
+          <t>exte_ch17</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4175,7 +4203,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 19 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 17 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -4187,7 +4215,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>exte_ch20</t>
+          <t>exte_ch18</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -4202,7 +4230,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 20 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 18 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4214,7 +4242,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>exte_ch21</t>
+          <t>exte_ch19</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4229,7 +4257,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 21 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 19 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -4241,7 +4269,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>exte_ch22</t>
+          <t>exte_ch20</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -4256,7 +4284,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 22 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 20 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -4268,7 +4296,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>exte_ch23</t>
+          <t>exte_ch21</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4283,7 +4311,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 23 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 21 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -4295,7 +4323,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>exte_ch24</t>
+          <t>exte_ch22</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -4310,7 +4338,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 24 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 22 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -4322,7 +4350,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>exte_ch25</t>
+          <t>exte_ch23</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4337,7 +4365,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 25 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 23 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -4349,7 +4377,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>exte_ch26</t>
+          <t>exte_ch24</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -4364,7 +4392,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 26 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 24 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -4376,7 +4404,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>exte_ch27</t>
+          <t>exte_ch25</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4391,7 +4419,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 27 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 25 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -4403,7 +4431,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>exte_ch28</t>
+          <t>exte_ch26</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -4418,7 +4446,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 28 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 26 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -4430,7 +4458,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>exte_ch29</t>
+          <t>exte_ch27</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4445,7 +4473,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 29 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 27 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -4457,7 +4485,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>exte_ch30</t>
+          <t>exte_ch28</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -4472,7 +4500,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 30 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 28 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -4484,7 +4512,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>exte_ch31</t>
+          <t>exte_ch29</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4499,7 +4527,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 31 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 29 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -4511,7 +4539,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>exte_ch32</t>
+          <t>exte_ch30</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -4526,7 +4554,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 32 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 30 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -4538,7 +4566,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>exte_ch33</t>
+          <t>exte_ch31</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4553,7 +4581,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 33 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 31 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -4565,7 +4593,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>exte_ch34</t>
+          <t>exte_ch32</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -4580,7 +4608,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 34 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 32 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -4592,7 +4620,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>exte_ch35</t>
+          <t>exte_ch33</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4607,7 +4635,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 35 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 33 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -4619,7 +4647,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>exte_ch36</t>
+          <t>exte_ch34</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -4634,7 +4662,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 36 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 34 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -4646,7 +4674,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>exte_ch37</t>
+          <t>exte_ch35</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4661,7 +4689,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 37 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 35 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -4673,7 +4701,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>exte_ch38</t>
+          <t>exte_ch36</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -4688,7 +4716,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 38 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 36 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -4700,7 +4728,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>exte_ch39</t>
+          <t>exte_ch37</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4715,7 +4743,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 39 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 37 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -4727,7 +4755,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>exte_ch40</t>
+          <t>exte_ch38</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -4742,7 +4770,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 40 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 38 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -4754,7 +4782,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>exte_ch41</t>
+          <t>exte_ch39</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4769,7 +4797,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 41 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 39 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -4781,7 +4809,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>exte_ch42</t>
+          <t>exte_ch40</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -4796,7 +4824,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 42 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 40 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -4808,7 +4836,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>exte_ch43</t>
+          <t>exte_ch41</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4823,7 +4851,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 43 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 41 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -4835,7 +4863,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>exte_ch44</t>
+          <t>exte_ch42</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -4850,7 +4878,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 44 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 42 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -4862,7 +4890,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>exte_ch45</t>
+          <t>exte_ch43</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4877,7 +4905,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 45 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 43 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -4889,7 +4917,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>exte_ch46</t>
+          <t>exte_ch44</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -4904,7 +4932,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 46 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 44 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -4916,7 +4944,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>exte_ch47</t>
+          <t>exte_ch45</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4931,7 +4959,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 47 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 45 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -4943,7 +4971,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>exte_ch48</t>
+          <t>exte_ch46</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -4958,7 +4986,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 48 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 46 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -4970,7 +4998,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>exte_ch49</t>
+          <t>exte_ch47</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4985,7 +5013,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 49 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 47 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -4997,7 +5025,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>exte_ch50</t>
+          <t>exte_ch48</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -5012,7 +5040,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 50 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 48 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -5024,7 +5052,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>exte_ch51</t>
+          <t>exte_ch49</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5039,7 +5067,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 51 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 49 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -5051,7 +5079,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>exte_ch52</t>
+          <t>exte_ch50</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -5066,7 +5094,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 52 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 50 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -5078,7 +5106,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>exte_ch53</t>
+          <t>exte_ch51</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5093,7 +5121,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 53 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 51 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -5105,7 +5133,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>exte_ch54</t>
+          <t>exte_ch52</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -5120,7 +5148,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 54 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 52 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -5132,7 +5160,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>exte_ch55</t>
+          <t>exte_ch53</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5147,7 +5175,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 55 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 53 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -5159,7 +5187,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>exte_ch56</t>
+          <t>exte_ch54</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -5174,7 +5202,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 56 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 54 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -5186,7 +5214,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>exte_ch57</t>
+          <t>exte_ch55</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5201,7 +5229,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 57 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 55 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -5213,7 +5241,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>exte_ch58</t>
+          <t>exte_ch56</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -5228,7 +5256,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 58 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 56 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -5240,7 +5268,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>exte_ch59</t>
+          <t>exte_ch57</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5255,7 +5283,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 59 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 57 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -5267,7 +5295,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>exte_ch60</t>
+          <t>exte_ch58</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -5282,7 +5310,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 60 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 58 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -5294,7 +5322,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>exte_ch61</t>
+          <t>exte_ch59</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5309,7 +5337,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 61 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 59 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -5321,7 +5349,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>exte_ch62</t>
+          <t>exte_ch60</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -5336,7 +5364,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 62 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 60 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -5348,7 +5376,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>exte_ch63</t>
+          <t>exte_ch61</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5363,7 +5391,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>HD-sEMG channel 63 placed over forearm extensor muscles</t>
+          <t>HD-sEMG channel 61 placed over forearm extensor muscles</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -5375,25 +5403,79 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
+          <t>exte_ch62</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>FLOAT64</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>uV / Digital</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>HD-sEMG channel 62 placed over forearm extensor muscles</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>exte_ch63</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>FLOAT64</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>uV / Digital</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>HD-sEMG channel 63 placed over forearm extensor muscles</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
           <t>exte_ch64</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>FLOAT64</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>uV / Digital</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>FLOAT64</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>uV / Digital</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>HD-sEMG channel 64 placed over forearm extensor muscles</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5410,11 +5492,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="73" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -5450,49 +5532,49 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>task_id</t>
+          <t>kin_id</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Alphanumeric</t>
+          <t>UUID v4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>References the task/trial execution</t>
+          <t>Unique identifier for the kinematic 3D metadata entry</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>subject_id</t>
+          <t>recording_id</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Alphanumeric</t>
+          <t>UUID v4</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>References the participant</t>
+          <t>References the recording session</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -5504,49 +5586,49 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>fnum</t>
+          <t>equipment_id</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Frame Index</t>
+          <t>Alphanumeric</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sequential temporal frame index</t>
+          <t>References the kinematic acquisition equipment</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>wrist_x</t>
+          <t>file_path</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Relative Path</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Wrist</t>
+          <t>Relative file path to the 3D kinematics CSV file</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -5558,22 +5640,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>wrist_y</t>
+          <t>fnum</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Frame Index</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Wrist</t>
+          <t>Sequential temporal frame index</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -5585,7 +5667,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>wrist_z</t>
+          <t>wrist_x</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -5600,7 +5682,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Wrist</t>
+          <t>3D spatial X coordinate for Wrist</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -5612,7 +5694,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>wrist_error</t>
+          <t>wrist_y</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -5622,12 +5704,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Wrist</t>
+          <t>3D spatial Y coordinate for Wrist</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -5639,22 +5721,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>wrist_ncams</t>
+          <t>wrist_z</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Wrist</t>
+          <t>3D spatial Z coordinate for Wrist</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -5666,7 +5748,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>wrist_score</t>
+          <t>wrist_error</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -5676,12 +5758,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Wrist</t>
+          <t>Reprojection error in 2D pixels for Wrist</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -5693,22 +5775,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>thumb_cmc_x</t>
+          <t>wrist_ncams</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Thumb Cmc</t>
+          <t>Number of cameras contributing to triangulation for Wrist</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5720,7 +5802,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>thumb_cmc_y</t>
+          <t>wrist_score</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5730,12 +5812,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Thumb Cmc</t>
+          <t>Minimum 2D detection confidence score for Wrist</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -5747,7 +5829,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>thumb_cmc_z</t>
+          <t>thumb_cmc_x</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -5762,7 +5844,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Thumb Cmc</t>
+          <t>3D spatial X coordinate for Thumb Cmc</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5774,7 +5856,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>thumb_cmc_error</t>
+          <t>thumb_cmc_y</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -5784,12 +5866,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Thumb Cmc</t>
+          <t>3D spatial Y coordinate for Thumb Cmc</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -5801,22 +5883,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>thumb_cmc_ncams</t>
+          <t>thumb_cmc_z</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Thumb Cmc</t>
+          <t>3D spatial Z coordinate for Thumb Cmc</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -5828,7 +5910,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>thumb_cmc_score</t>
+          <t>thumb_cmc_error</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -5838,12 +5920,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Thumb Cmc</t>
+          <t>Reprojection error in 2D pixels for Thumb Cmc</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -5855,22 +5937,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>thumb_mcp_x</t>
+          <t>thumb_cmc_ncams</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Thumb Mcp</t>
+          <t>Number of cameras contributing to triangulation for Thumb Cmc</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -5882,7 +5964,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>thumb_mcp_y</t>
+          <t>thumb_cmc_score</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -5892,12 +5974,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Thumb Mcp</t>
+          <t>Minimum 2D detection confidence score for Thumb Cmc</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -5909,7 +5991,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>thumb_mcp_z</t>
+          <t>thumb_mcp_x</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -5924,7 +6006,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Thumb Mcp</t>
+          <t>3D spatial X coordinate for Thumb Mcp</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -5936,7 +6018,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>thumb_mcp_error</t>
+          <t>thumb_mcp_y</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -5946,12 +6028,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Thumb Mcp</t>
+          <t>3D spatial Y coordinate for Thumb Mcp</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -5963,22 +6045,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>thumb_mcp_ncams</t>
+          <t>thumb_mcp_z</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Thumb Mcp</t>
+          <t>3D spatial Z coordinate for Thumb Mcp</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -5990,7 +6072,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>thumb_mcp_score</t>
+          <t>thumb_mcp_error</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -6000,12 +6082,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Thumb Mcp</t>
+          <t>Reprojection error in 2D pixels for Thumb Mcp</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -6017,22 +6099,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>thumb_ip_x</t>
+          <t>thumb_mcp_ncams</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Thumb Ip</t>
+          <t>Number of cameras contributing to triangulation for Thumb Mcp</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6044,7 +6126,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>thumb_ip_y</t>
+          <t>thumb_mcp_score</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6054,12 +6136,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Thumb Ip</t>
+          <t>Minimum 2D detection confidence score for Thumb Mcp</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -6071,7 +6153,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>thumb_ip_z</t>
+          <t>thumb_ip_x</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -6086,7 +6168,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Thumb Ip</t>
+          <t>3D spatial X coordinate for Thumb Ip</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6098,7 +6180,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>thumb_ip_error</t>
+          <t>thumb_ip_y</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6108,12 +6190,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Thumb Ip</t>
+          <t>3D spatial Y coordinate for Thumb Ip</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -6125,22 +6207,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>thumb_ip_ncams</t>
+          <t>thumb_ip_z</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Thumb Ip</t>
+          <t>3D spatial Z coordinate for Thumb Ip</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -6152,7 +6234,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>thumb_ip_score</t>
+          <t>thumb_ip_error</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6162,12 +6244,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Thumb Ip</t>
+          <t>Reprojection error in 2D pixels for Thumb Ip</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -6179,22 +6261,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>thumb_tip_x</t>
+          <t>thumb_ip_ncams</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Thumb Tip</t>
+          <t>Number of cameras contributing to triangulation for Thumb Ip</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -6206,7 +6288,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>thumb_tip_y</t>
+          <t>thumb_ip_score</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6216,12 +6298,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Thumb Tip</t>
+          <t>Minimum 2D detection confidence score for Thumb Ip</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -6233,7 +6315,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>thumb_tip_z</t>
+          <t>thumb_tip_x</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -6248,7 +6330,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Thumb Tip</t>
+          <t>3D spatial X coordinate for Thumb Tip</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -6260,7 +6342,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>thumb_tip_error</t>
+          <t>thumb_tip_y</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -6270,12 +6352,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Thumb Tip</t>
+          <t>3D spatial Y coordinate for Thumb Tip</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -6287,22 +6369,22 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>thumb_tip_ncams</t>
+          <t>thumb_tip_z</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Thumb Tip</t>
+          <t>3D spatial Z coordinate for Thumb Tip</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6314,7 +6396,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>thumb_tip_score</t>
+          <t>thumb_tip_error</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -6324,12 +6406,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Thumb Tip</t>
+          <t>Reprojection error in 2D pixels for Thumb Tip</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -6341,22 +6423,22 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>index_finger_mcp_x</t>
+          <t>thumb_tip_ncams</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Index Finger Mcp</t>
+          <t>Number of cameras contributing to triangulation for Thumb Tip</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -6368,7 +6450,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>index_finger_mcp_y</t>
+          <t>thumb_tip_score</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -6378,12 +6460,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Index Finger Mcp</t>
+          <t>Minimum 2D detection confidence score for Thumb Tip</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6395,7 +6477,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>index_finger_mcp_z</t>
+          <t>index_finger_mcp_x</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -6410,7 +6492,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Index Finger Mcp</t>
+          <t>3D spatial X coordinate for Index Finger Mcp</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6422,7 +6504,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>index_finger_mcp_error</t>
+          <t>index_finger_mcp_y</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -6432,12 +6514,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Index Finger Mcp</t>
+          <t>3D spatial Y coordinate for Index Finger Mcp</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6449,22 +6531,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>index_finger_mcp_ncams</t>
+          <t>index_finger_mcp_z</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Index Finger Mcp</t>
+          <t>3D spatial Z coordinate for Index Finger Mcp</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -6476,7 +6558,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>index_finger_mcp_score</t>
+          <t>index_finger_mcp_error</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -6486,12 +6568,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Index Finger Mcp</t>
+          <t>Reprojection error in 2D pixels for Index Finger Mcp</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6503,22 +6585,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>index_finger_pip_x</t>
+          <t>index_finger_mcp_ncams</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Index Finger Pip</t>
+          <t>Number of cameras contributing to triangulation for Index Finger Mcp</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -6530,7 +6612,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>index_finger_pip_y</t>
+          <t>index_finger_mcp_score</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -6540,12 +6622,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Index Finger Pip</t>
+          <t>Minimum 2D detection confidence score for Index Finger Mcp</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -6557,7 +6639,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>index_finger_pip_z</t>
+          <t>index_finger_pip_x</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -6572,7 +6654,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Index Finger Pip</t>
+          <t>3D spatial X coordinate for Index Finger Pip</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -6584,7 +6666,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>index_finger_pip_error</t>
+          <t>index_finger_pip_y</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -6594,12 +6676,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Index Finger Pip</t>
+          <t>3D spatial Y coordinate for Index Finger Pip</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -6611,22 +6693,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>index_finger_pip_ncams</t>
+          <t>index_finger_pip_z</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Index Finger Pip</t>
+          <t>3D spatial Z coordinate for Index Finger Pip</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -6638,7 +6720,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>index_finger_pip_score</t>
+          <t>index_finger_pip_error</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -6648,12 +6730,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Index Finger Pip</t>
+          <t>Reprojection error in 2D pixels for Index Finger Pip</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6665,22 +6747,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>index_finger_dip_x</t>
+          <t>index_finger_pip_ncams</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Index Finger Dip</t>
+          <t>Number of cameras contributing to triangulation for Index Finger Pip</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -6692,7 +6774,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>index_finger_dip_y</t>
+          <t>index_finger_pip_score</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -6702,12 +6784,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Index Finger Dip</t>
+          <t>Minimum 2D detection confidence score for Index Finger Pip</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -6719,7 +6801,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>index_finger_dip_z</t>
+          <t>index_finger_dip_x</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -6734,7 +6816,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Index Finger Dip</t>
+          <t>3D spatial X coordinate for Index Finger Dip</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -6746,7 +6828,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>index_finger_dip_error</t>
+          <t>index_finger_dip_y</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -6756,12 +6838,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Index Finger Dip</t>
+          <t>3D spatial Y coordinate for Index Finger Dip</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -6773,22 +6855,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>index_finger_dip_ncams</t>
+          <t>index_finger_dip_z</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Index Finger Dip</t>
+          <t>3D spatial Z coordinate for Index Finger Dip</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -6800,7 +6882,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>index_finger_dip_score</t>
+          <t>index_finger_dip_error</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -6810,12 +6892,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Index Finger Dip</t>
+          <t>Reprojection error in 2D pixels for Index Finger Dip</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -6827,22 +6909,22 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>index_finger_tip_x</t>
+          <t>index_finger_dip_ncams</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Index Finger Tip</t>
+          <t>Number of cameras contributing to triangulation for Index Finger Dip</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -6854,7 +6936,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>index_finger_tip_y</t>
+          <t>index_finger_dip_score</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -6864,12 +6946,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Index Finger Tip</t>
+          <t>Minimum 2D detection confidence score for Index Finger Dip</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6881,7 +6963,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>index_finger_tip_z</t>
+          <t>index_finger_tip_x</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -6896,7 +6978,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Index Finger Tip</t>
+          <t>3D spatial X coordinate for Index Finger Tip</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -6908,7 +6990,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>index_finger_tip_error</t>
+          <t>index_finger_tip_y</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -6918,12 +7000,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Index Finger Tip</t>
+          <t>3D spatial Y coordinate for Index Finger Tip</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -6935,22 +7017,22 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>index_finger_tip_ncams</t>
+          <t>index_finger_tip_z</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Index Finger Tip</t>
+          <t>3D spatial Z coordinate for Index Finger Tip</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -6962,7 +7044,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>index_finger_tip_score</t>
+          <t>index_finger_tip_error</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -6972,12 +7054,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Index Finger Tip</t>
+          <t>Reprojection error in 2D pixels for Index Finger Tip</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -6989,22 +7071,22 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_mcp_x</t>
+          <t>index_finger_tip_ncams</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Middle Finger Mcp</t>
+          <t>Number of cameras contributing to triangulation for Index Finger Tip</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -7016,7 +7098,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_mcp_y</t>
+          <t>index_finger_tip_score</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -7026,12 +7108,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Middle Finger Mcp</t>
+          <t>Minimum 2D detection confidence score for Index Finger Tip</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -7043,7 +7125,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_mcp_z</t>
+          <t>middle_finger_mcp_x</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -7058,7 +7140,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Middle Finger Mcp</t>
+          <t>3D spatial X coordinate for Middle Finger Mcp</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -7070,7 +7152,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_mcp_error</t>
+          <t>middle_finger_mcp_y</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -7080,12 +7162,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Middle Finger Mcp</t>
+          <t>3D spatial Y coordinate for Middle Finger Mcp</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -7097,22 +7179,22 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_mcp_ncams</t>
+          <t>middle_finger_mcp_z</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Middle Finger Mcp</t>
+          <t>3D spatial Z coordinate for Middle Finger Mcp</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -7124,7 +7206,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_mcp_score</t>
+          <t>middle_finger_mcp_error</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -7134,12 +7216,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Middle Finger Mcp</t>
+          <t>Reprojection error in 2D pixels for Middle Finger Mcp</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -7151,22 +7233,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_pip_x</t>
+          <t>middle_finger_mcp_ncams</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Middle Finger Pip</t>
+          <t>Number of cameras contributing to triangulation for Middle Finger Mcp</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -7178,7 +7260,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_pip_y</t>
+          <t>middle_finger_mcp_score</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -7188,12 +7270,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Middle Finger Pip</t>
+          <t>Minimum 2D detection confidence score for Middle Finger Mcp</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -7205,7 +7287,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_pip_z</t>
+          <t>middle_finger_pip_x</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -7220,7 +7302,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Middle Finger Pip</t>
+          <t>3D spatial X coordinate for Middle Finger Pip</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -7232,7 +7314,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_pip_error</t>
+          <t>middle_finger_pip_y</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -7242,12 +7324,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Middle Finger Pip</t>
+          <t>3D spatial Y coordinate for Middle Finger Pip</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -7259,22 +7341,22 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_pip_ncams</t>
+          <t>middle_finger_pip_z</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Middle Finger Pip</t>
+          <t>3D spatial Z coordinate for Middle Finger Pip</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -7286,7 +7368,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_pip_score</t>
+          <t>middle_finger_pip_error</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -7296,12 +7378,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Middle Finger Pip</t>
+          <t>Reprojection error in 2D pixels for Middle Finger Pip</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -7313,22 +7395,22 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_dip_x</t>
+          <t>middle_finger_pip_ncams</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Middle Finger Dip</t>
+          <t>Number of cameras contributing to triangulation for Middle Finger Pip</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -7340,7 +7422,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_dip_y</t>
+          <t>middle_finger_pip_score</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -7350,12 +7432,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Middle Finger Dip</t>
+          <t>Minimum 2D detection confidence score for Middle Finger Pip</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -7367,7 +7449,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_dip_z</t>
+          <t>middle_finger_dip_x</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -7382,7 +7464,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Middle Finger Dip</t>
+          <t>3D spatial X coordinate for Middle Finger Dip</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -7394,7 +7476,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_dip_error</t>
+          <t>middle_finger_dip_y</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7404,12 +7486,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Middle Finger Dip</t>
+          <t>3D spatial Y coordinate for Middle Finger Dip</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -7421,22 +7503,22 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_dip_ncams</t>
+          <t>middle_finger_dip_z</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Middle Finger Dip</t>
+          <t>3D spatial Z coordinate for Middle Finger Dip</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -7448,7 +7530,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_dip_score</t>
+          <t>middle_finger_dip_error</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7458,12 +7540,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Middle Finger Dip</t>
+          <t>Reprojection error in 2D pixels for Middle Finger Dip</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -7475,22 +7557,22 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_tip_x</t>
+          <t>middle_finger_dip_ncams</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Middle Finger Tip</t>
+          <t>Number of cameras contributing to triangulation for Middle Finger Dip</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -7502,7 +7584,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_tip_y</t>
+          <t>middle_finger_dip_score</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7512,12 +7594,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Middle Finger Tip</t>
+          <t>Minimum 2D detection confidence score for Middle Finger Dip</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -7529,7 +7611,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_tip_z</t>
+          <t>middle_finger_tip_x</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -7544,7 +7626,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Middle Finger Tip</t>
+          <t>3D spatial X coordinate for Middle Finger Tip</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -7556,7 +7638,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_tip_error</t>
+          <t>middle_finger_tip_y</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7566,12 +7648,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Middle Finger Tip</t>
+          <t>3D spatial Y coordinate for Middle Finger Tip</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -7583,22 +7665,22 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>middle_finger_tip_ncams</t>
+          <t>middle_finger_tip_z</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Middle Finger Tip</t>
+          <t>3D spatial Z coordinate for Middle Finger Tip</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -7610,7 +7692,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>middle_finger_tip_score</t>
+          <t>middle_finger_tip_error</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7620,12 +7702,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Middle Finger Tip</t>
+          <t>Reprojection error in 2D pixels for Middle Finger Tip</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -7637,22 +7719,22 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_mcp_x</t>
+          <t>middle_finger_tip_ncams</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Ring Finger Mcp</t>
+          <t>Number of cameras contributing to triangulation for Middle Finger Tip</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -7664,7 +7746,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_mcp_y</t>
+          <t>middle_finger_tip_score</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7674,12 +7756,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Ring Finger Mcp</t>
+          <t>Minimum 2D detection confidence score for Middle Finger Tip</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7691,7 +7773,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_mcp_z</t>
+          <t>ring_finger_mcp_x</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -7706,7 +7788,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Ring Finger Mcp</t>
+          <t>3D spatial X coordinate for Ring Finger Mcp</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -7718,7 +7800,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_mcp_error</t>
+          <t>ring_finger_mcp_y</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -7728,12 +7810,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Ring Finger Mcp</t>
+          <t>3D spatial Y coordinate for Ring Finger Mcp</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -7745,22 +7827,22 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_mcp_ncams</t>
+          <t>ring_finger_mcp_z</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Ring Finger Mcp</t>
+          <t>3D spatial Z coordinate for Ring Finger Mcp</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -7772,7 +7854,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_mcp_score</t>
+          <t>ring_finger_mcp_error</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -7782,12 +7864,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Ring Finger Mcp</t>
+          <t>Reprojection error in 2D pixels for Ring Finger Mcp</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -7799,22 +7881,22 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_pip_x</t>
+          <t>ring_finger_mcp_ncams</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Ring Finger Pip</t>
+          <t>Number of cameras contributing to triangulation for Ring Finger Mcp</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -7826,7 +7908,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_pip_y</t>
+          <t>ring_finger_mcp_score</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -7836,12 +7918,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Ring Finger Pip</t>
+          <t>Minimum 2D detection confidence score for Ring Finger Mcp</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -7853,7 +7935,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_pip_z</t>
+          <t>ring_finger_pip_x</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -7868,7 +7950,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Ring Finger Pip</t>
+          <t>3D spatial X coordinate for Ring Finger Pip</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -7880,7 +7962,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_pip_error</t>
+          <t>ring_finger_pip_y</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -7890,12 +7972,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Ring Finger Pip</t>
+          <t>3D spatial Y coordinate for Ring Finger Pip</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -7907,22 +7989,22 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_pip_ncams</t>
+          <t>ring_finger_pip_z</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Ring Finger Pip</t>
+          <t>3D spatial Z coordinate for Ring Finger Pip</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -7934,7 +8016,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_pip_score</t>
+          <t>ring_finger_pip_error</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -7944,12 +8026,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Ring Finger Pip</t>
+          <t>Reprojection error in 2D pixels for Ring Finger Pip</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -7961,22 +8043,22 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_dip_x</t>
+          <t>ring_finger_pip_ncams</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Ring Finger Dip</t>
+          <t>Number of cameras contributing to triangulation for Ring Finger Pip</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -7988,7 +8070,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_dip_y</t>
+          <t>ring_finger_pip_score</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -7998,12 +8080,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Ring Finger Dip</t>
+          <t>Minimum 2D detection confidence score for Ring Finger Pip</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -8015,7 +8097,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_dip_z</t>
+          <t>ring_finger_dip_x</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -8030,7 +8112,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Ring Finger Dip</t>
+          <t>3D spatial X coordinate for Ring Finger Dip</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -8042,7 +8124,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_dip_error</t>
+          <t>ring_finger_dip_y</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -8052,12 +8134,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Ring Finger Dip</t>
+          <t>3D spatial Y coordinate for Ring Finger Dip</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -8069,22 +8151,22 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_dip_ncams</t>
+          <t>ring_finger_dip_z</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Ring Finger Dip</t>
+          <t>3D spatial Z coordinate for Ring Finger Dip</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -8096,7 +8178,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_dip_score</t>
+          <t>ring_finger_dip_error</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -8106,12 +8188,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Ring Finger Dip</t>
+          <t>Reprojection error in 2D pixels for Ring Finger Dip</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -8123,22 +8205,22 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_tip_x</t>
+          <t>ring_finger_dip_ncams</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Ring Finger Tip</t>
+          <t>Number of cameras contributing to triangulation for Ring Finger Dip</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -8150,7 +8232,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_tip_y</t>
+          <t>ring_finger_dip_score</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -8160,12 +8242,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Ring Finger Tip</t>
+          <t>Minimum 2D detection confidence score for Ring Finger Dip</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -8177,7 +8259,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_tip_z</t>
+          <t>ring_finger_tip_x</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -8192,7 +8274,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Ring Finger Tip</t>
+          <t>3D spatial X coordinate for Ring Finger Tip</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -8204,7 +8286,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_tip_error</t>
+          <t>ring_finger_tip_y</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -8214,12 +8296,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Ring Finger Tip</t>
+          <t>3D spatial Y coordinate for Ring Finger Tip</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -8231,22 +8313,22 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>ring_finger_tip_ncams</t>
+          <t>ring_finger_tip_z</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Ring Finger Tip</t>
+          <t>3D spatial Z coordinate for Ring Finger Tip</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -8258,7 +8340,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ring_finger_tip_score</t>
+          <t>ring_finger_tip_error</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -8268,12 +8350,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Ring Finger Tip</t>
+          <t>Reprojection error in 2D pixels for Ring Finger Tip</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -8285,22 +8367,22 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>pinky_mcp_x</t>
+          <t>ring_finger_tip_ncams</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Pinky Mcp</t>
+          <t>Number of cameras contributing to triangulation for Ring Finger Tip</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -8312,7 +8394,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>pinky_mcp_y</t>
+          <t>ring_finger_tip_score</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -8322,12 +8404,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Pinky Mcp</t>
+          <t>Minimum 2D detection confidence score for Ring Finger Tip</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -8339,7 +8421,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>pinky_mcp_z</t>
+          <t>pinky_mcp_x</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -8354,7 +8436,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Pinky Mcp</t>
+          <t>3D spatial X coordinate for Pinky Mcp</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -8366,7 +8448,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>pinky_mcp_error</t>
+          <t>pinky_mcp_y</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -8376,12 +8458,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Pinky Mcp</t>
+          <t>3D spatial Y coordinate for Pinky Mcp</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -8393,22 +8475,22 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>pinky_mcp_ncams</t>
+          <t>pinky_mcp_z</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Pinky Mcp</t>
+          <t>3D spatial Z coordinate for Pinky Mcp</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -8420,7 +8502,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>pinky_mcp_score</t>
+          <t>pinky_mcp_error</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -8430,12 +8512,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Pinky Mcp</t>
+          <t>Reprojection error in 2D pixels for Pinky Mcp</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -8447,22 +8529,22 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>pinky_pip_x</t>
+          <t>pinky_mcp_ncams</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Pinky Pip</t>
+          <t>Number of cameras contributing to triangulation for Pinky Mcp</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -8474,7 +8556,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>pinky_pip_y</t>
+          <t>pinky_mcp_score</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -8484,12 +8566,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Pinky Pip</t>
+          <t>Minimum 2D detection confidence score for Pinky Mcp</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -8501,7 +8583,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>pinky_pip_z</t>
+          <t>pinky_pip_x</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -8516,7 +8598,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Pinky Pip</t>
+          <t>3D spatial X coordinate for Pinky Pip</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -8528,7 +8610,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>pinky_pip_error</t>
+          <t>pinky_pip_y</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -8538,12 +8620,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Pinky Pip</t>
+          <t>3D spatial Y coordinate for Pinky Pip</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -8555,22 +8637,22 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>pinky_pip_ncams</t>
+          <t>pinky_pip_z</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Pinky Pip</t>
+          <t>3D spatial Z coordinate for Pinky Pip</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -8582,7 +8664,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>pinky_pip_score</t>
+          <t>pinky_pip_error</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -8592,12 +8674,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Pinky Pip</t>
+          <t>Reprojection error in 2D pixels for Pinky Pip</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -8609,22 +8691,22 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>pinky_dip_x</t>
+          <t>pinky_pip_ncams</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Pinky Dip</t>
+          <t>Number of cameras contributing to triangulation for Pinky Pip</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -8636,7 +8718,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>pinky_dip_y</t>
+          <t>pinky_pip_score</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -8646,12 +8728,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Pinky Dip</t>
+          <t>Minimum 2D detection confidence score for Pinky Pip</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -8663,7 +8745,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>pinky_dip_z</t>
+          <t>pinky_dip_x</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -8678,7 +8760,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Pinky Dip</t>
+          <t>3D spatial X coordinate for Pinky Dip</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -8690,7 +8772,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>pinky_dip_error</t>
+          <t>pinky_dip_y</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -8700,12 +8782,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Pinky Dip</t>
+          <t>3D spatial Y coordinate for Pinky Dip</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -8717,22 +8799,22 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>pinky_dip_ncams</t>
+          <t>pinky_dip_z</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Pinky Dip</t>
+          <t>3D spatial Z coordinate for Pinky Dip</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -8744,7 +8826,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>pinky_dip_score</t>
+          <t>pinky_dip_error</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8754,12 +8836,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Pinky Dip</t>
+          <t>Reprojection error in 2D pixels for Pinky Dip</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -8771,22 +8853,22 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>pinky_tip_x</t>
+          <t>pinky_dip_ncams</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>3D spatial X coordinate for Pinky Tip</t>
+          <t>Number of cameras contributing to triangulation for Pinky Dip</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -8798,7 +8880,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>pinky_tip_y</t>
+          <t>pinky_dip_score</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -8808,12 +8890,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>mm / px</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>3D spatial Y coordinate for Pinky Tip</t>
+          <t>Minimum 2D detection confidence score for Pinky Dip</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -8825,7 +8907,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>pinky_tip_z</t>
+          <t>pinky_tip_x</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -8840,7 +8922,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>3D spatial Z coordinate for Pinky Tip</t>
+          <t>3D spatial X coordinate for Pinky Tip</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -8852,7 +8934,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>pinky_tip_error</t>
+          <t>pinky_tip_y</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -8862,12 +8944,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Pixels (px)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Reprojection error in 2D pixels for Pinky Tip</t>
+          <t>3D spatial Y coordinate for Pinky Tip</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -8879,22 +8961,22 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>pinky_tip_ncams</t>
+          <t>pinky_tip_z</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>INT64</t>
+          <t>FLOAT64</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Count (0-5)</t>
+          <t>mm / px</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Number of cameras contributing to triangulation for Pinky Tip</t>
+          <t>3D spatial Z coordinate for Pinky Tip</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -8906,7 +8988,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>pinky_tip_score</t>
+          <t>pinky_tip_error</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -8916,12 +8998,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Score (0-1)</t>
+          <t>Pixels (px)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2D detection confidence score for Pinky Tip</t>
+          <t>Reprojection error in 2D pixels for Pinky Tip</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -8933,22 +9015,22 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>m_00</t>
+          <t>pinky_tip_ncams</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>FLOAT64</t>
+          <t>INT64</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Matrix Element</t>
+          <t>Count (0-5)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Element (0,0) of the 3x3 coordinate rotation matrix M</t>
+          <t>Number of cameras contributing to triangulation for Pinky Tip</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -8960,7 +9042,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>m_01</t>
+          <t>pinky_tip_score</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8970,12 +9052,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Matrix Element</t>
+          <t>Score (0-1)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Element (0,1) of the 3x3 coordinate rotation matrix M</t>
+          <t>Minimum 2D detection confidence score for Pinky Tip</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -8987,7 +9069,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>m_02</t>
+          <t>m_00</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -9002,7 +9084,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Element (0,2) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (0,0) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -9014,7 +9096,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>m_10</t>
+          <t>m_01</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9029,7 +9111,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Element (1,0) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (0,1) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -9041,7 +9123,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>m_11</t>
+          <t>m_02</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -9056,7 +9138,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Element (1,1) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (0,2) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -9068,7 +9150,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>m_12</t>
+          <t>m_10</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9083,7 +9165,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Element (1,2) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (1,0) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -9095,7 +9177,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>m_20</t>
+          <t>m_11</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -9110,7 +9192,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Element (2,0) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (1,1) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -9122,7 +9204,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>m_21</t>
+          <t>m_12</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9137,7 +9219,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Element (2,1) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (1,2) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -9149,7 +9231,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>m_22</t>
+          <t>m_20</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -9164,7 +9246,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Element (2,2) of the 3x3 coordinate rotation matrix M</t>
+          <t>Element (2,0) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -9176,7 +9258,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>center_0</t>
+          <t>m_21</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9186,12 +9268,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Spatial Coords</t>
+          <t>Matrix Element</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Coordinate 0 of the 3D reference system origin center</t>
+          <t>Element (2,1) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -9203,7 +9285,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>center_1</t>
+          <t>m_22</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -9213,12 +9295,12 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Spatial Coords</t>
+          <t>Matrix Element</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Coordinate 1 of the 3D reference system origin center</t>
+          <t>Element (2,2) of the 3x3 coordinate rotation matrix M</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -9230,25 +9312,235 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>center_0</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>FLOAT64</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Spatial Coords</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Coordinate 0 of the 3D reference system origin center</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>center_1</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>FLOAT64</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Spatial Coords</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Coordinate 1 of the 3D reference system origin center</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
           <t>center_2</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>FLOAT64</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>FLOAT64</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>Spatial Coords</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Coordinate 2 of the 3D reference system origin center</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="67" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unit/Format</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>video_id</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>UUID v4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Unique identifier for the 3D reconstructed video metadata entry</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>recording_id</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>UUID v4</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>References the recording session</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>fps</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Frames per second</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Frame rate of the reconstructed MP4 video</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>file_path</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Relative Path</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Relative file path to the 3D reconstructed MP4 video file</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
